--- a/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5797233325452635</v>
+        <v>0.448217265783928</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8184125010643337</v>
+        <v>0.4190236593387163</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5795034061106561</v>
+        <v>0.4482010240418387</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8182377613758646</v>
+        <v>0.4190146636870872</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4190945628687204</v>
+        <v>0.5409434015892545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7268062088406571</v>
+        <v>0.5102943184381789</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9971162146262075</v>
+        <v>0.9865822908165129</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9988275071371554</v>
+        <v>0.9808363252499813</v>
       </c>
       <c r="I2" t="n">
-        <v>0.761</v>
+        <v>0.439</v>
       </c>
     </row>
   </sheetData>
